--- a/data/trans_orig/IP16A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Edad-trans_orig.xlsx
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>30528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46807</t>
+          <t>46761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59239</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42927</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77827</t>
+          <t>77784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94887</t>
+          <t>94301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43702</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>89801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89414</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109213</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183996</t>
+          <t>182190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>210777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94069</t>
+          <t>94594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>123181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62544</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29674</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>40196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40214</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58280</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116583</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29986</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61726</t>
+          <t>60214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>31099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55085</t>
+          <t>53753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69165</t>
+          <t>69904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41707</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>68356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>113111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75407</t>
+          <t>74293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133075</t>
+          <t>131950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119965</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>191488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244269</t>
+          <t>243782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170871</t>
+          <t>168428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,47 +1066,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,47 +1409,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,47 +1752,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,47 +2095,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26654</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22108</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31587</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26913</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22161</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30528</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21752</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30403</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>73,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26654</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20589</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30864</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>69,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46761</t>
+          <t>47037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11772</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16318</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14336</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14745</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11772</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7562</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17837</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42432</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54771</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>37673</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31774</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42713</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31250</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42621</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>69,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48988</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>43353</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>54919</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77784</t>
+          <t>78354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94301</t>
+          <t>94383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18377</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12594</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24933</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16492</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22391</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11544</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22915</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18377</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12446</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>24012</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13746</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9098</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17878</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14839</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10246</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18780</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10219</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19335</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13746</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18160</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18817</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>14127</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10186</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18720</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9631</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18747</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14169</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9755</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18487</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28966</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28966</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28966</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9559</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5922</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19261</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15024</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22634</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14741</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22599</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9559</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5946</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22451</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34564</t>
+          <t>35180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15309</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11072</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18946</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7908</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12428</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15309</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>18922</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88618</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>108340</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89801</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>108483</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>107709</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88910</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>109578</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182190</t>
+          <t>184488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210777</t>
+          <t>211108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50234</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69956</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>48111</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38314</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56996</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57689</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,77%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>59627</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>48996</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69664</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94594</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123181</t>
+          <t>120883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>16757</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12457</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20062</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>16913</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12876</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20455</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13057</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20392</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16757</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12956</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19731</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7219</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11519</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10120</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14157</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6641</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13976</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4245</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11020</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27241</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21981</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31937</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>28359</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23423</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33074</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33129</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>27241</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21383</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31990</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>63,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>48017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>62205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15855</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11159</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21115</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13880</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9165</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18788</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15855</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11106</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>21713</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,79%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12961</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18048</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23607</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18477</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28015</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18383</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28159</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12961</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8352</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20485</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15398</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24652</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>12517</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8109</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17647</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7965</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17741</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20485</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15521</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25094</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40196</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6879</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15097</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9334</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5649</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13338</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13444</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11021</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15307</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15879</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12731</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8727</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16416</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8621</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16536</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11737</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7451</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15618</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58624</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77455</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>68501</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86885</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>68124</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86669</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>58903</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76857</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132523</t>
+          <t>133087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157678</t>
+          <t>158295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>55297</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>64652</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>49249</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40576</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58960</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40792</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>59337</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>55297</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>46419</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>64373</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12471</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9810</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14642</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10216</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7057</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13004</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29961</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4962</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2791</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5767</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8926</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22409</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31244</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21575</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15524</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27423</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,28%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>47300</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60214</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13987</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18826</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25048</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19200</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31099</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43072</t>
+          <t>34831</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52894</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26058</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20135</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31603</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14637</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24618</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37323</t>
+          <t>37561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17913</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12368</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23836</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12533</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22514</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45997</t>
+          <t>44358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32386</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40242</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>52641</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34583</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69904</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>44,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25588</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>86672</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68356</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113111</t>
+          <t>72277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29927</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22071</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38162</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8053</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43374</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>61229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>87974</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>110339</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>85806</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131950</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120047</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191488</t>
+          <t>161358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>243782</t>
+          <t>190697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66790</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>76978</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>73697</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>45765</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91909</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>65014</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>55643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>148337</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>117247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168428</t>
+          <t>146586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
